--- a/proyectos_diseno/BASES_DE_DATOS/Equipos_Proyectos.xlsx
+++ b/proyectos_diseno/BASES_DE_DATOS/Equipos_Proyectos.xlsx
@@ -1194,27 +1194,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>e895250b-1093-4fdd-a1a4-1f9cdbe0afb8</t>
+          <t>1b11f9e9-d1f3-4586-8be7-990592339e54</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
+          <t>53103afd-00df-4b44-83cd-6f0b650262cd</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0c3035a4-0958-46da-bb6a-88fd92c84028</t>
+          <t>549fb86e-275a-4fe4-bcc0-9b6a3d61ad16</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ELL</t>
+          <t>FDV</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ESTACION DE LLENADO DE BIG BAGS</t>
+          <t>FILTRO DE VENTEO</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>no_estandar</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>fc0d355f-d0a6-4c3a-8fa7-1003f9c8872c</t>
+          <t>cf6b4aa9-6068-4431-877d-5bee0d5c376a</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8006035d-6a3a-4fd1-8b8a-3a3adf304f29</t>
+          <t>0c3035a4-0958-46da-bb6a-88fd92c84028</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>TLV</t>
+          <t>ELL</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>TOLVA RECEPTORA</t>
+          <t>ESTACION DE LLENADO DE BIG BAGS</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>no_estandar</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>cdfa8039-f56f-43fa-bf52-389f08229f25</t>
+          <t>dae509ae-cee9-425d-9d48-d304f7b82047</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>76ac91f7-77ec-451a-8813-e7e049d8e070</t>
+          <t>8006035d-6a3a-4fd1-8b8a-3a3adf304f29</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>RDT</t>
+          <t>TLV</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ROMPEDOR DE TERRONES</t>
+          <t>TOLVA RECEPTORA</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1298,37 +1298,37 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>estandar</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1b11f9e9-d1f3-4586-8be7-990592339e54</t>
+          <t>bcb36622-6811-44b9-999d-3fd76069b5cb</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>53103afd-00df-4b44-83cd-6f0b650262cd</t>
+          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>549fb86e-275a-4fe4-bcc0-9b6a3d61ad16</t>
+          <t>76ac91f7-77ec-451a-8813-e7e049d8e070</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>FDV</t>
+          <t>RDT</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>FILTRO DE VENTEO</t>
+          <t>ROMPEDOR DE TERRONES</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1336,11 +1336,11 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>medio</t>
+          <t>estandar</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
